--- a/data/exports/watchlist_g1.xlsx
+++ b/data/exports/watchlist_g1.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>46307.78751088463</v>
+        <v>46308.66744142296</v>
       </c>
     </row>
   </sheetData>
